--- a/des.xlsx
+++ b/des.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\dansong\scripts\sharepoint-projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527677E8-9B2D-40D4-BCB3-29AD0DA97652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26089AB4-40F1-4EF7-AAC7-679902EF3AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{92E3EBA7-43B6-496B-B436-BAFA5D8BAC06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="676">
   <si>
     <t>1/1/1</t>
   </si>
@@ -797,822 +797,6 @@
     <t>interfaces</t>
   </si>
   <si>
-    <t>172/1/001</t>
-  </si>
-  <si>
-    <t>172/1/002</t>
-  </si>
-  <si>
-    <t>172/1/003</t>
-  </si>
-  <si>
-    <t>172/1/004</t>
-  </si>
-  <si>
-    <t>172/1/005</t>
-  </si>
-  <si>
-    <t>172/1/006</t>
-  </si>
-  <si>
-    <t>172/1/007</t>
-  </si>
-  <si>
-    <t>172/1/008</t>
-  </si>
-  <si>
-    <t>172/1/009</t>
-  </si>
-  <si>
-    <t>172/1/010</t>
-  </si>
-  <si>
-    <t>172/1/011</t>
-  </si>
-  <si>
-    <t>172/1/012</t>
-  </si>
-  <si>
-    <t>172/1/013</t>
-  </si>
-  <si>
-    <t>172/1/014</t>
-  </si>
-  <si>
-    <t>172/1/015</t>
-  </si>
-  <si>
-    <t>172/1/016</t>
-  </si>
-  <si>
-    <t>172/1/017</t>
-  </si>
-  <si>
-    <t>172/1/018</t>
-  </si>
-  <si>
-    <t>172/1/019</t>
-  </si>
-  <si>
-    <t>172/1/020</t>
-  </si>
-  <si>
-    <t>172/1/021</t>
-  </si>
-  <si>
-    <t>172/1/022</t>
-  </si>
-  <si>
-    <t>172/1/023</t>
-  </si>
-  <si>
-    <t>172/1/024</t>
-  </si>
-  <si>
-    <t>172/1/025</t>
-  </si>
-  <si>
-    <t>172/1/026</t>
-  </si>
-  <si>
-    <t>172/1/027</t>
-  </si>
-  <si>
-    <t>172/1/028</t>
-  </si>
-  <si>
-    <t>172/1/029</t>
-  </si>
-  <si>
-    <t>172/1/030</t>
-  </si>
-  <si>
-    <t>172/1/031</t>
-  </si>
-  <si>
-    <t>172/1/032</t>
-  </si>
-  <si>
-    <t>172/1/033</t>
-  </si>
-  <si>
-    <t>172/1/034</t>
-  </si>
-  <si>
-    <t>172/1/035</t>
-  </si>
-  <si>
-    <t>172/1/036</t>
-  </si>
-  <si>
-    <t>172/1/037</t>
-  </si>
-  <si>
-    <t>172/1/038</t>
-  </si>
-  <si>
-    <t>172/1/039</t>
-  </si>
-  <si>
-    <t>172/1/040</t>
-  </si>
-  <si>
-    <t>172/1/041</t>
-  </si>
-  <si>
-    <t>172/1/042</t>
-  </si>
-  <si>
-    <t>172/1/043</t>
-  </si>
-  <si>
-    <t>172/1/044</t>
-  </si>
-  <si>
-    <t>172/1/045</t>
-  </si>
-  <si>
-    <t>172/1/046</t>
-  </si>
-  <si>
-    <t>172/1/047</t>
-  </si>
-  <si>
-    <t>172/1/048</t>
-  </si>
-  <si>
-    <t>172/1/049</t>
-  </si>
-  <si>
-    <t>172/1/050</t>
-  </si>
-  <si>
-    <t>172/1/051</t>
-  </si>
-  <si>
-    <t>172/1/052</t>
-  </si>
-  <si>
-    <t>172/1/053</t>
-  </si>
-  <si>
-    <t>172/1/054</t>
-  </si>
-  <si>
-    <t>172/1/055</t>
-  </si>
-  <si>
-    <t>172/1/056</t>
-  </si>
-  <si>
-    <t>172/1/057</t>
-  </si>
-  <si>
-    <t>172/1/058</t>
-  </si>
-  <si>
-    <t>172/1/059</t>
-  </si>
-  <si>
-    <t>172/1/060</t>
-  </si>
-  <si>
-    <t>172/1/061</t>
-  </si>
-  <si>
-    <t>172/1/062</t>
-  </si>
-  <si>
-    <t>172/1/063</t>
-  </si>
-  <si>
-    <t>172/1/064</t>
-  </si>
-  <si>
-    <t>172/1/065</t>
-  </si>
-  <si>
-    <t>172/1/066</t>
-  </si>
-  <si>
-    <t>172/1/067</t>
-  </si>
-  <si>
-    <t>172/1/068</t>
-  </si>
-  <si>
-    <t>172/1/069</t>
-  </si>
-  <si>
-    <t>172/1/070</t>
-  </si>
-  <si>
-    <t>172/1/071</t>
-  </si>
-  <si>
-    <t>172/1/072</t>
-  </si>
-  <si>
-    <t>172/1/073</t>
-  </si>
-  <si>
-    <t>172/1/074</t>
-  </si>
-  <si>
-    <t>172/1/075</t>
-  </si>
-  <si>
-    <t>172/1/076</t>
-  </si>
-  <si>
-    <t>172/1/077</t>
-  </si>
-  <si>
-    <t>172/1/078</t>
-  </si>
-  <si>
-    <t>172/1/079</t>
-  </si>
-  <si>
-    <t>172/1/080</t>
-  </si>
-  <si>
-    <t>172/1/081</t>
-  </si>
-  <si>
-    <t>172/1/082</t>
-  </si>
-  <si>
-    <t>172/1/083</t>
-  </si>
-  <si>
-    <t>172/1/084</t>
-  </si>
-  <si>
-    <t>172/1/085</t>
-  </si>
-  <si>
-    <t>172/1/086</t>
-  </si>
-  <si>
-    <t>172/1/087</t>
-  </si>
-  <si>
-    <t>172/1/088</t>
-  </si>
-  <si>
-    <t>172/1/089</t>
-  </si>
-  <si>
-    <t>172/1/090</t>
-  </si>
-  <si>
-    <t>172/1/091</t>
-  </si>
-  <si>
-    <t>172/1/092</t>
-  </si>
-  <si>
-    <t>172/1/093</t>
-  </si>
-  <si>
-    <t>172/1/094</t>
-  </si>
-  <si>
-    <t>172/1/095</t>
-  </si>
-  <si>
-    <t>172/1/096</t>
-  </si>
-  <si>
-    <t>172/1/097</t>
-  </si>
-  <si>
-    <t>172/1/098</t>
-  </si>
-  <si>
-    <t>172/1/099</t>
-  </si>
-  <si>
-    <t>172/1/100</t>
-  </si>
-  <si>
-    <t>172/1/101</t>
-  </si>
-  <si>
-    <t>172/1/102</t>
-  </si>
-  <si>
-    <t>172/1/103</t>
-  </si>
-  <si>
-    <t>172/1/104</t>
-  </si>
-  <si>
-    <t>172/1/105</t>
-  </si>
-  <si>
-    <t>172/1/106</t>
-  </si>
-  <si>
-    <t>172/1/107</t>
-  </si>
-  <si>
-    <t>172/1/108</t>
-  </si>
-  <si>
-    <t>172/1/109</t>
-  </si>
-  <si>
-    <t>172/1/110</t>
-  </si>
-  <si>
-    <t>172/1/111</t>
-  </si>
-  <si>
-    <t>172/1/112</t>
-  </si>
-  <si>
-    <t>172/1/113</t>
-  </si>
-  <si>
-    <t>172/1/114</t>
-  </si>
-  <si>
-    <t>172/1/115</t>
-  </si>
-  <si>
-    <t>172/1/116</t>
-  </si>
-  <si>
-    <t>172/1/117</t>
-  </si>
-  <si>
-    <t>172/1/118</t>
-  </si>
-  <si>
-    <t>172/1/119</t>
-  </si>
-  <si>
-    <t>172/1/120</t>
-  </si>
-  <si>
-    <t>172/1/121</t>
-  </si>
-  <si>
-    <t>172/1/122</t>
-  </si>
-  <si>
-    <t>172/1/123</t>
-  </si>
-  <si>
-    <t>172/1/124</t>
-  </si>
-  <si>
-    <t>172/1/125</t>
-  </si>
-  <si>
-    <t>172/1/126</t>
-  </si>
-  <si>
-    <t>172/1/127</t>
-  </si>
-  <si>
-    <t>172/1/128</t>
-  </si>
-  <si>
-    <t>172/1/129</t>
-  </si>
-  <si>
-    <t>172/1/130</t>
-  </si>
-  <si>
-    <t>172/1/131</t>
-  </si>
-  <si>
-    <t>172/1/132</t>
-  </si>
-  <si>
-    <t>172/1/133</t>
-  </si>
-  <si>
-    <t>172/1/134</t>
-  </si>
-  <si>
-    <t>172/1/135</t>
-  </si>
-  <si>
-    <t>172/1/136</t>
-  </si>
-  <si>
-    <t>172/1/137</t>
-  </si>
-  <si>
-    <t>172/1/138</t>
-  </si>
-  <si>
-    <t>172/1/139</t>
-  </si>
-  <si>
-    <t>172/1/140</t>
-  </si>
-  <si>
-    <t>172/1/141</t>
-  </si>
-  <si>
-    <t>172/1/142</t>
-  </si>
-  <si>
-    <t>172/1/143</t>
-  </si>
-  <si>
-    <t>172/1/144</t>
-  </si>
-  <si>
-    <t>172/1/145</t>
-  </si>
-  <si>
-    <t>172/1/146</t>
-  </si>
-  <si>
-    <t>172/1/147</t>
-  </si>
-  <si>
-    <t>172/1/148</t>
-  </si>
-  <si>
-    <t>172/1/149</t>
-  </si>
-  <si>
-    <t>172/1/150</t>
-  </si>
-  <si>
-    <t>172/1/151</t>
-  </si>
-  <si>
-    <t>172/1/152</t>
-  </si>
-  <si>
-    <t>172/1/153</t>
-  </si>
-  <si>
-    <t>172/1/154</t>
-  </si>
-  <si>
-    <t>172/1/155</t>
-  </si>
-  <si>
-    <t>172/1/156</t>
-  </si>
-  <si>
-    <t>172/1/157</t>
-  </si>
-  <si>
-    <t>172/1/158</t>
-  </si>
-  <si>
-    <t>172/1/159</t>
-  </si>
-  <si>
-    <t>172/1/160</t>
-  </si>
-  <si>
-    <t>172/1/161</t>
-  </si>
-  <si>
-    <t>172/1/162</t>
-  </si>
-  <si>
-    <t>172/1/163</t>
-  </si>
-  <si>
-    <t>172/1/164</t>
-  </si>
-  <si>
-    <t>172/1/165</t>
-  </si>
-  <si>
-    <t>172/1/166</t>
-  </si>
-  <si>
-    <t>172/1/167</t>
-  </si>
-  <si>
-    <t>172/1/168</t>
-  </si>
-  <si>
-    <t>172/1/169</t>
-  </si>
-  <si>
-    <t>172/1/170</t>
-  </si>
-  <si>
-    <t>172/1/171</t>
-  </si>
-  <si>
-    <t>172/1/172</t>
-  </si>
-  <si>
-    <t>172/1/173</t>
-  </si>
-  <si>
-    <t>172/1/174</t>
-  </si>
-  <si>
-    <t>172/1/175</t>
-  </si>
-  <si>
-    <t>172/1/176</t>
-  </si>
-  <si>
-    <t>172/1/177</t>
-  </si>
-  <si>
-    <t>172/1/178</t>
-  </si>
-  <si>
-    <t>172/1/179</t>
-  </si>
-  <si>
-    <t>172/1/180</t>
-  </si>
-  <si>
-    <t>172/1/181</t>
-  </si>
-  <si>
-    <t>172/1/182</t>
-  </si>
-  <si>
-    <t>172/1/183</t>
-  </si>
-  <si>
-    <t>172/1/184</t>
-  </si>
-  <si>
-    <t>172/1/185</t>
-  </si>
-  <si>
-    <t>172/1/186</t>
-  </si>
-  <si>
-    <t>172/1/187</t>
-  </si>
-  <si>
-    <t>172/1/188</t>
-  </si>
-  <si>
-    <t>172/1/189</t>
-  </si>
-  <si>
-    <t>172/1/190</t>
-  </si>
-  <si>
-    <t>172/1/191</t>
-  </si>
-  <si>
-    <t>172/1/192</t>
-  </si>
-  <si>
-    <t>172/1/193</t>
-  </si>
-  <si>
-    <t>172/1/194</t>
-  </si>
-  <si>
-    <t>172/1/195</t>
-  </si>
-  <si>
-    <t>172/1/196</t>
-  </si>
-  <si>
-    <t>172/1/197</t>
-  </si>
-  <si>
-    <t>172/1/198</t>
-  </si>
-  <si>
-    <t>172/1/199</t>
-  </si>
-  <si>
-    <t>172/1/200</t>
-  </si>
-  <si>
-    <t>172/1/201</t>
-  </si>
-  <si>
-    <t>172/1/202</t>
-  </si>
-  <si>
-    <t>172/1/203</t>
-  </si>
-  <si>
-    <t>172/1/204</t>
-  </si>
-  <si>
-    <t>172/1/205</t>
-  </si>
-  <si>
-    <t>172/1/206</t>
-  </si>
-  <si>
-    <t>172/1/207</t>
-  </si>
-  <si>
-    <t>172/1/208</t>
-  </si>
-  <si>
-    <t>172/1/209</t>
-  </si>
-  <si>
-    <t>172/1/210</t>
-  </si>
-  <si>
-    <t>172/1/211</t>
-  </si>
-  <si>
-    <t>172/1/212</t>
-  </si>
-  <si>
-    <t>172/1/213</t>
-  </si>
-  <si>
-    <t>172/1/214</t>
-  </si>
-  <si>
-    <t>172/1/215</t>
-  </si>
-  <si>
-    <t>172/1/216</t>
-  </si>
-  <si>
-    <t>172/1/217</t>
-  </si>
-  <si>
-    <t>172/1/218</t>
-  </si>
-  <si>
-    <t>172/1/219</t>
-  </si>
-  <si>
-    <t>172/1/220</t>
-  </si>
-  <si>
-    <t>172/1/221</t>
-  </si>
-  <si>
-    <t>172/1/222</t>
-  </si>
-  <si>
-    <t>172/1/223</t>
-  </si>
-  <si>
-    <t>172/1/224</t>
-  </si>
-  <si>
-    <t>172/1/225</t>
-  </si>
-  <si>
-    <t>172/1/226</t>
-  </si>
-  <si>
-    <t>172/1/227</t>
-  </si>
-  <si>
-    <t>172/1/228</t>
-  </si>
-  <si>
-    <t>172/1/229</t>
-  </si>
-  <si>
-    <t>172/1/230</t>
-  </si>
-  <si>
-    <t>172/1/231</t>
-  </si>
-  <si>
-    <t>172/1/232</t>
-  </si>
-  <si>
-    <t>172/1/233</t>
-  </si>
-  <si>
-    <t>172/1/234</t>
-  </si>
-  <si>
-    <t>172/1/235</t>
-  </si>
-  <si>
-    <t>172/1/236</t>
-  </si>
-  <si>
-    <t>172/1/237</t>
-  </si>
-  <si>
-    <t>172/1/238</t>
-  </si>
-  <si>
-    <t>172/1/239</t>
-  </si>
-  <si>
-    <t>172/1/240</t>
-  </si>
-  <si>
-    <t>172/1/241</t>
-  </si>
-  <si>
-    <t>172/1/242</t>
-  </si>
-  <si>
-    <t>172/1/243</t>
-  </si>
-  <si>
-    <t>172/1/244</t>
-  </si>
-  <si>
-    <t>172/1/245</t>
-  </si>
-  <si>
-    <t>172/1/246</t>
-  </si>
-  <si>
-    <t>172/1/247</t>
-  </si>
-  <si>
-    <t>172/1/248</t>
-  </si>
-  <si>
-    <t>172/1/249</t>
-  </si>
-  <si>
-    <t>172/1/250</t>
-  </si>
-  <si>
-    <t>172/1/251</t>
-  </si>
-  <si>
-    <t>172/1/252</t>
-  </si>
-  <si>
-    <t>172/1/253</t>
-  </si>
-  <si>
-    <t>172/1/254</t>
-  </si>
-  <si>
-    <t>172/1/255</t>
-  </si>
-  <si>
-    <t>172/1/256</t>
-  </si>
-  <si>
-    <t>172/1/257</t>
-  </si>
-  <si>
-    <t>172/1/258</t>
-  </si>
-  <si>
-    <t>172/1/259</t>
-  </si>
-  <si>
-    <t>172/1/260</t>
-  </si>
-  <si>
-    <t>172/1/261</t>
-  </si>
-  <si>
-    <t>172/1/262</t>
-  </si>
-  <si>
-    <t>172/1/263</t>
-  </si>
-  <si>
-    <t>172/1/264</t>
-  </si>
-  <si>
-    <t>172/1/265</t>
-  </si>
-  <si>
-    <t>172/1/266</t>
-  </si>
-  <si>
-    <t>172/1/267</t>
-  </si>
-  <si>
-    <t>172/1/268</t>
-  </si>
-  <si>
-    <t>172/1/269</t>
-  </si>
-  <si>
-    <t>172/1/270</t>
-  </si>
-  <si>
-    <t>172/1/271</t>
-  </si>
-  <si>
-    <t>172/1/272</t>
-  </si>
-  <si>
     <t>6/1/21</t>
   </si>
   <si>
@@ -1655,54 +839,6 @@
     <t>6/1/47</t>
   </si>
   <si>
-    <t>172/1/273</t>
-  </si>
-  <si>
-    <t>172/1/274</t>
-  </si>
-  <si>
-    <t>172/1/275</t>
-  </si>
-  <si>
-    <t>172/1/276</t>
-  </si>
-  <si>
-    <t>172/1/277</t>
-  </si>
-  <si>
-    <t>172/1/278</t>
-  </si>
-  <si>
-    <t>172/1/279</t>
-  </si>
-  <si>
-    <t>172/1/280</t>
-  </si>
-  <si>
-    <t>172/1/281</t>
-  </si>
-  <si>
-    <t>172/1/282</t>
-  </si>
-  <si>
-    <t>172/1/283</t>
-  </si>
-  <si>
-    <t>172/1/284</t>
-  </si>
-  <si>
-    <t>172/1/285</t>
-  </si>
-  <si>
-    <t>172/1/286</t>
-  </si>
-  <si>
-    <t>172/1/287</t>
-  </si>
-  <si>
-    <t>172/1/288</t>
-  </si>
-  <si>
     <t>6/1/2</t>
   </si>
   <si>
@@ -1776,6 +912,1158 @@
   </si>
   <si>
     <t>172.22.22.2</t>
+  </si>
+  <si>
+    <t>387/10/001</t>
+  </si>
+  <si>
+    <t>387/10/002</t>
+  </si>
+  <si>
+    <t>387/10/003</t>
+  </si>
+  <si>
+    <t>387/10/004</t>
+  </si>
+  <si>
+    <t>387/10/005</t>
+  </si>
+  <si>
+    <t>387/10/006</t>
+  </si>
+  <si>
+    <t>387/10/007</t>
+  </si>
+  <si>
+    <t>387/10/008</t>
+  </si>
+  <si>
+    <t>387/10/009</t>
+  </si>
+  <si>
+    <t>387/10/010</t>
+  </si>
+  <si>
+    <t>387/10/011</t>
+  </si>
+  <si>
+    <t>387/10/012</t>
+  </si>
+  <si>
+    <t>387/10/013</t>
+  </si>
+  <si>
+    <t>387/10/014</t>
+  </si>
+  <si>
+    <t>387/10/015</t>
+  </si>
+  <si>
+    <t>387/10/016</t>
+  </si>
+  <si>
+    <t>387/10/017</t>
+  </si>
+  <si>
+    <t>387/10/018</t>
+  </si>
+  <si>
+    <t>387/10/019</t>
+  </si>
+  <si>
+    <t>387/10/020</t>
+  </si>
+  <si>
+    <t>387/10/021</t>
+  </si>
+  <si>
+    <t>387/10/022</t>
+  </si>
+  <si>
+    <t>387/10/023</t>
+  </si>
+  <si>
+    <t>387/10/024</t>
+  </si>
+  <si>
+    <t>387/10/025</t>
+  </si>
+  <si>
+    <t>387/10/026</t>
+  </si>
+  <si>
+    <t>387/10/027</t>
+  </si>
+  <si>
+    <t>387/10/028</t>
+  </si>
+  <si>
+    <t>387/10/029</t>
+  </si>
+  <si>
+    <t>387/10/030</t>
+  </si>
+  <si>
+    <t>387/10/031</t>
+  </si>
+  <si>
+    <t>387/10/032</t>
+  </si>
+  <si>
+    <t>387/10/033</t>
+  </si>
+  <si>
+    <t>387/10/034</t>
+  </si>
+  <si>
+    <t>387/10/035</t>
+  </si>
+  <si>
+    <t>387/10/036</t>
+  </si>
+  <si>
+    <t>387/10/037</t>
+  </si>
+  <si>
+    <t>387/10/038</t>
+  </si>
+  <si>
+    <t>387/10/039</t>
+  </si>
+  <si>
+    <t>387/10/040</t>
+  </si>
+  <si>
+    <t>387/10/041</t>
+  </si>
+  <si>
+    <t>387/10/042</t>
+  </si>
+  <si>
+    <t>387/10/043</t>
+  </si>
+  <si>
+    <t>387/10/044</t>
+  </si>
+  <si>
+    <t>387/10/045</t>
+  </si>
+  <si>
+    <t>387/10/046</t>
+  </si>
+  <si>
+    <t>387/10/047</t>
+  </si>
+  <si>
+    <t>387/10/048</t>
+  </si>
+  <si>
+    <t>387/10/049</t>
+  </si>
+  <si>
+    <t>387/10/050</t>
+  </si>
+  <si>
+    <t>387/10/051</t>
+  </si>
+  <si>
+    <t>387/10/052</t>
+  </si>
+  <si>
+    <t>387/10/053</t>
+  </si>
+  <si>
+    <t>387/10/054</t>
+  </si>
+  <si>
+    <t>387/10/055</t>
+  </si>
+  <si>
+    <t>387/10/056</t>
+  </si>
+  <si>
+    <t>387/10/057</t>
+  </si>
+  <si>
+    <t>387/10/058</t>
+  </si>
+  <si>
+    <t>387/10/059</t>
+  </si>
+  <si>
+    <t>387/10/060</t>
+  </si>
+  <si>
+    <t>387/10/061</t>
+  </si>
+  <si>
+    <t>387/10/062</t>
+  </si>
+  <si>
+    <t>387/10/063</t>
+  </si>
+  <si>
+    <t>387/10/064</t>
+  </si>
+  <si>
+    <t>387/10/065</t>
+  </si>
+  <si>
+    <t>387/10/066</t>
+  </si>
+  <si>
+    <t>387/10/067</t>
+  </si>
+  <si>
+    <t>387/10/068</t>
+  </si>
+  <si>
+    <t>387/10/069</t>
+  </si>
+  <si>
+    <t>387/10/070</t>
+  </si>
+  <si>
+    <t>387/10/071</t>
+  </si>
+  <si>
+    <t>387/10/072</t>
+  </si>
+  <si>
+    <t>387/10/073</t>
+  </si>
+  <si>
+    <t>387/10/074</t>
+  </si>
+  <si>
+    <t>387/10/075</t>
+  </si>
+  <si>
+    <t>387/10/076</t>
+  </si>
+  <si>
+    <t>387/10/077</t>
+  </si>
+  <si>
+    <t>387/10/078</t>
+  </si>
+  <si>
+    <t>387/10/079</t>
+  </si>
+  <si>
+    <t>387/10/080</t>
+  </si>
+  <si>
+    <t>387/10/081</t>
+  </si>
+  <si>
+    <t>387/10/082</t>
+  </si>
+  <si>
+    <t>387/10/083</t>
+  </si>
+  <si>
+    <t>387/10/084</t>
+  </si>
+  <si>
+    <t>387/10/085</t>
+  </si>
+  <si>
+    <t>387/10/086</t>
+  </si>
+  <si>
+    <t>387/10/087</t>
+  </si>
+  <si>
+    <t>387/10/088</t>
+  </si>
+  <si>
+    <t>387/10/089</t>
+  </si>
+  <si>
+    <t>387/10/090</t>
+  </si>
+  <si>
+    <t>387/10/091</t>
+  </si>
+  <si>
+    <t>387/10/092</t>
+  </si>
+  <si>
+    <t>387/10/093</t>
+  </si>
+  <si>
+    <t>387/10/094</t>
+  </si>
+  <si>
+    <t>387/10/095</t>
+  </si>
+  <si>
+    <t>387/10/096</t>
+  </si>
+  <si>
+    <t>387/10/097</t>
+  </si>
+  <si>
+    <t>387/10/098</t>
+  </si>
+  <si>
+    <t>387/10/099</t>
+  </si>
+  <si>
+    <t>387/10/100</t>
+  </si>
+  <si>
+    <t>387/10/101</t>
+  </si>
+  <si>
+    <t>387/10/102</t>
+  </si>
+  <si>
+    <t>387/10/103</t>
+  </si>
+  <si>
+    <t>387/10/104</t>
+  </si>
+  <si>
+    <t>387/10/105</t>
+  </si>
+  <si>
+    <t>387/10/106</t>
+  </si>
+  <si>
+    <t>387/10/107</t>
+  </si>
+  <si>
+    <t>387/10/108</t>
+  </si>
+  <si>
+    <t>387/10/109</t>
+  </si>
+  <si>
+    <t>387/10/110</t>
+  </si>
+  <si>
+    <t>387/10/111</t>
+  </si>
+  <si>
+    <t>387/10/112</t>
+  </si>
+  <si>
+    <t>387/10/113</t>
+  </si>
+  <si>
+    <t>387/10/114</t>
+  </si>
+  <si>
+    <t>387/10/115</t>
+  </si>
+  <si>
+    <t>387/10/116</t>
+  </si>
+  <si>
+    <t>387/10/117</t>
+  </si>
+  <si>
+    <t>387/10/118</t>
+  </si>
+  <si>
+    <t>387/10/119</t>
+  </si>
+  <si>
+    <t>387/10/120</t>
+  </si>
+  <si>
+    <t>387/10/121</t>
+  </si>
+  <si>
+    <t>387/10/122</t>
+  </si>
+  <si>
+    <t>387/10/123</t>
+  </si>
+  <si>
+    <t>387/10/124</t>
+  </si>
+  <si>
+    <t>387/10/125</t>
+  </si>
+  <si>
+    <t>387/10/126</t>
+  </si>
+  <si>
+    <t>387/10/127</t>
+  </si>
+  <si>
+    <t>387/10/128</t>
+  </si>
+  <si>
+    <t>387/10/129</t>
+  </si>
+  <si>
+    <t>387/10/130</t>
+  </si>
+  <si>
+    <t>387/10/131</t>
+  </si>
+  <si>
+    <t>387/10/132</t>
+  </si>
+  <si>
+    <t>387/10/133</t>
+  </si>
+  <si>
+    <t>387/10/134</t>
+  </si>
+  <si>
+    <t>387/10/135</t>
+  </si>
+  <si>
+    <t>387/10/136</t>
+  </si>
+  <si>
+    <t>387/10/137</t>
+  </si>
+  <si>
+    <t>387/10/138</t>
+  </si>
+  <si>
+    <t>387/10/139</t>
+  </si>
+  <si>
+    <t>387/10/140</t>
+  </si>
+  <si>
+    <t>387/10/141</t>
+  </si>
+  <si>
+    <t>387/10/142</t>
+  </si>
+  <si>
+    <t>387/10/143</t>
+  </si>
+  <si>
+    <t>387/10/144</t>
+  </si>
+  <si>
+    <t>387/10/145</t>
+  </si>
+  <si>
+    <t>387/10/146</t>
+  </si>
+  <si>
+    <t>387/10/147</t>
+  </si>
+  <si>
+    <t>387/10/148</t>
+  </si>
+  <si>
+    <t>387/10/149</t>
+  </si>
+  <si>
+    <t>387/10/150</t>
+  </si>
+  <si>
+    <t>387/10/151</t>
+  </si>
+  <si>
+    <t>387/10/152</t>
+  </si>
+  <si>
+    <t>387/10/153</t>
+  </si>
+  <si>
+    <t>387/10/154</t>
+  </si>
+  <si>
+    <t>387/10/155</t>
+  </si>
+  <si>
+    <t>387/10/156</t>
+  </si>
+  <si>
+    <t>387/10/157</t>
+  </si>
+  <si>
+    <t>387/10/158</t>
+  </si>
+  <si>
+    <t>387/10/159</t>
+  </si>
+  <si>
+    <t>387/10/160</t>
+  </si>
+  <si>
+    <t>387/10/161</t>
+  </si>
+  <si>
+    <t>387/10/162</t>
+  </si>
+  <si>
+    <t>387/10/163</t>
+  </si>
+  <si>
+    <t>387/10/164</t>
+  </si>
+  <si>
+    <t>387/10/165</t>
+  </si>
+  <si>
+    <t>387/10/166</t>
+  </si>
+  <si>
+    <t>387/10/167</t>
+  </si>
+  <si>
+    <t>387/10/168</t>
+  </si>
+  <si>
+    <t>387/10/169</t>
+  </si>
+  <si>
+    <t>387/10/170</t>
+  </si>
+  <si>
+    <t>387/10/171</t>
+  </si>
+  <si>
+    <t>387/10/172</t>
+  </si>
+  <si>
+    <t>387/10/173</t>
+  </si>
+  <si>
+    <t>387/10/174</t>
+  </si>
+  <si>
+    <t>387/10/175</t>
+  </si>
+  <si>
+    <t>387/10/176</t>
+  </si>
+  <si>
+    <t>387/10/177</t>
+  </si>
+  <si>
+    <t>387/10/178</t>
+  </si>
+  <si>
+    <t>387/10/179</t>
+  </si>
+  <si>
+    <t>387/10/180</t>
+  </si>
+  <si>
+    <t>387/10/181</t>
+  </si>
+  <si>
+    <t>387/10/182</t>
+  </si>
+  <si>
+    <t>387/10/183</t>
+  </si>
+  <si>
+    <t>387/10/184</t>
+  </si>
+  <si>
+    <t>387/10/185</t>
+  </si>
+  <si>
+    <t>387/10/186</t>
+  </si>
+  <si>
+    <t>387/10/187</t>
+  </si>
+  <si>
+    <t>387/10/188</t>
+  </si>
+  <si>
+    <t>387/10/189</t>
+  </si>
+  <si>
+    <t>387/10/190</t>
+  </si>
+  <si>
+    <t>387/10/191</t>
+  </si>
+  <si>
+    <t>387/10/192</t>
+  </si>
+  <si>
+    <t>387/10/193</t>
+  </si>
+  <si>
+    <t>387/10/194</t>
+  </si>
+  <si>
+    <t>387/10/195</t>
+  </si>
+  <si>
+    <t>387/10/196</t>
+  </si>
+  <si>
+    <t>387/10/197</t>
+  </si>
+  <si>
+    <t>387/10/198</t>
+  </si>
+  <si>
+    <t>387/10/199</t>
+  </si>
+  <si>
+    <t>387/10/200</t>
+  </si>
+  <si>
+    <t>387/10/201</t>
+  </si>
+  <si>
+    <t>387/10/202</t>
+  </si>
+  <si>
+    <t>387/10/203</t>
+  </si>
+  <si>
+    <t>387/10/204</t>
+  </si>
+  <si>
+    <t>387/10/205</t>
+  </si>
+  <si>
+    <t>387/10/206</t>
+  </si>
+  <si>
+    <t>387/10/207</t>
+  </si>
+  <si>
+    <t>387/10/208</t>
+  </si>
+  <si>
+    <t>387/10/209</t>
+  </si>
+  <si>
+    <t>387/10/210</t>
+  </si>
+  <si>
+    <t>387/10/211</t>
+  </si>
+  <si>
+    <t>387/10/212</t>
+  </si>
+  <si>
+    <t>387/10/213</t>
+  </si>
+  <si>
+    <t>387/10/214</t>
+  </si>
+  <si>
+    <t>387/10/215</t>
+  </si>
+  <si>
+    <t>387/10/216</t>
+  </si>
+  <si>
+    <t>387/10/217</t>
+  </si>
+  <si>
+    <t>387/10/218</t>
+  </si>
+  <si>
+    <t>387/10/219</t>
+  </si>
+  <si>
+    <t>387/10/220</t>
+  </si>
+  <si>
+    <t>387/10/221</t>
+  </si>
+  <si>
+    <t>387/10/222</t>
+  </si>
+  <si>
+    <t>387/10/223</t>
+  </si>
+  <si>
+    <t>387/10/224</t>
+  </si>
+  <si>
+    <t>387/10/225</t>
+  </si>
+  <si>
+    <t>387/10/226</t>
+  </si>
+  <si>
+    <t>387/10/227</t>
+  </si>
+  <si>
+    <t>387/10/228</t>
+  </si>
+  <si>
+    <t>387/10/229</t>
+  </si>
+  <si>
+    <t>387/10/230</t>
+  </si>
+  <si>
+    <t>387/10/231</t>
+  </si>
+  <si>
+    <t>387/10/232</t>
+  </si>
+  <si>
+    <t>387/10/233</t>
+  </si>
+  <si>
+    <t>387/10/234</t>
+  </si>
+  <si>
+    <t>387/10/235</t>
+  </si>
+  <si>
+    <t>387/10/236</t>
+  </si>
+  <si>
+    <t>387/10/237</t>
+  </si>
+  <si>
+    <t>387/10/238</t>
+  </si>
+  <si>
+    <t>387/10/239</t>
+  </si>
+  <si>
+    <t>387/10/240</t>
+  </si>
+  <si>
+    <t>387/10/241</t>
+  </si>
+  <si>
+    <t>387/10/242</t>
+  </si>
+  <si>
+    <t>387/10/243</t>
+  </si>
+  <si>
+    <t>387/10/244</t>
+  </si>
+  <si>
+    <t>387/10/245</t>
+  </si>
+  <si>
+    <t>387/10/246</t>
+  </si>
+  <si>
+    <t>387/10/247</t>
+  </si>
+  <si>
+    <t>387/10/248</t>
+  </si>
+  <si>
+    <t>387/10/249</t>
+  </si>
+  <si>
+    <t>387/10/250</t>
+  </si>
+  <si>
+    <t>387/10/251</t>
+  </si>
+  <si>
+    <t>387/10/252</t>
+  </si>
+  <si>
+    <t>387/10/253</t>
+  </si>
+  <si>
+    <t>387/10/254</t>
+  </si>
+  <si>
+    <t>387/10/255</t>
+  </si>
+  <si>
+    <t>387/10/256</t>
+  </si>
+  <si>
+    <t>387/10/257</t>
+  </si>
+  <si>
+    <t>387/10/258</t>
+  </si>
+  <si>
+    <t>387/10/259</t>
+  </si>
+  <si>
+    <t>387/10/260</t>
+  </si>
+  <si>
+    <t>387/10/261</t>
+  </si>
+  <si>
+    <t>387/10/262</t>
+  </si>
+  <si>
+    <t>387/10/263</t>
+  </si>
+  <si>
+    <t>387/10/264</t>
+  </si>
+  <si>
+    <t>387/10/265</t>
+  </si>
+  <si>
+    <t>387/10/266</t>
+  </si>
+  <si>
+    <t>387/10/267</t>
+  </si>
+  <si>
+    <t>387/10/268</t>
+  </si>
+  <si>
+    <t>387/10/269</t>
+  </si>
+  <si>
+    <t>387/10/270</t>
+  </si>
+  <si>
+    <t>387/10/271</t>
+  </si>
+  <si>
+    <t>387/10/272</t>
+  </si>
+  <si>
+    <t>387/10/273</t>
+  </si>
+  <si>
+    <t>387/10/274</t>
+  </si>
+  <si>
+    <t>387/10/275</t>
+  </si>
+  <si>
+    <t>387/10/276</t>
+  </si>
+  <si>
+    <t>387/10/277</t>
+  </si>
+  <si>
+    <t>387/10/278</t>
+  </si>
+  <si>
+    <t>387/10/279</t>
+  </si>
+  <si>
+    <t>387/10/280</t>
+  </si>
+  <si>
+    <t>387/10/281</t>
+  </si>
+  <si>
+    <t>387/10/282</t>
+  </si>
+  <si>
+    <t>387/10/283</t>
+  </si>
+  <si>
+    <t>387/10/284</t>
+  </si>
+  <si>
+    <t>387/10/285</t>
+  </si>
+  <si>
+    <t>387/10/286</t>
+  </si>
+  <si>
+    <t>387/10/287</t>
+  </si>
+  <si>
+    <t>387/10/288</t>
+  </si>
+  <si>
+    <t>387/10/289</t>
+  </si>
+  <si>
+    <t>387/10/290</t>
+  </si>
+  <si>
+    <t>387/10/291</t>
+  </si>
+  <si>
+    <t>387/10/292</t>
+  </si>
+  <si>
+    <t>387/10/293</t>
+  </si>
+  <si>
+    <t>387/10/294</t>
+  </si>
+  <si>
+    <t>387/10/295</t>
+  </si>
+  <si>
+    <t>387/10/296</t>
+  </si>
+  <si>
+    <t>387/10/297</t>
+  </si>
+  <si>
+    <t>387/10/298</t>
+  </si>
+  <si>
+    <t>387/10/299</t>
+  </si>
+  <si>
+    <t>387/10/300</t>
+  </si>
+  <si>
+    <t>387/10/301</t>
+  </si>
+  <si>
+    <t>387/10/302</t>
+  </si>
+  <si>
+    <t>387/10/303</t>
+  </si>
+  <si>
+    <t>387/10/304</t>
+  </si>
+  <si>
+    <t>387/10/305</t>
+  </si>
+  <si>
+    <t>387/10/306</t>
+  </si>
+  <si>
+    <t>387/10/307</t>
+  </si>
+  <si>
+    <t>387/10/308</t>
+  </si>
+  <si>
+    <t>387/10/309</t>
+  </si>
+  <si>
+    <t>387/10/310</t>
+  </si>
+  <si>
+    <t>387/10/311</t>
+  </si>
+  <si>
+    <t>387/10/312</t>
+  </si>
+  <si>
+    <t>387/10/313</t>
+  </si>
+  <si>
+    <t>387/10/314</t>
+  </si>
+  <si>
+    <t>387/10/315</t>
+  </si>
+  <si>
+    <t>387/10/316</t>
+  </si>
+  <si>
+    <t>387/10/317</t>
+  </si>
+  <si>
+    <t>387/10/318</t>
+  </si>
+  <si>
+    <t>387/10/319</t>
+  </si>
+  <si>
+    <t>387/10/320</t>
+  </si>
+  <si>
+    <t>387/10/321</t>
+  </si>
+  <si>
+    <t>387/10/322</t>
+  </si>
+  <si>
+    <t>387/10/323</t>
+  </si>
+  <si>
+    <t>387/10/324</t>
+  </si>
+  <si>
+    <t>387/10/325</t>
+  </si>
+  <si>
+    <t>387/10/326</t>
+  </si>
+  <si>
+    <t>387/10/327</t>
+  </si>
+  <si>
+    <t>387/10/328</t>
+  </si>
+  <si>
+    <t>387/10/329</t>
+  </si>
+  <si>
+    <t>387/10/330</t>
+  </si>
+  <si>
+    <t>387/10/331</t>
+  </si>
+  <si>
+    <t>387/10/332</t>
+  </si>
+  <si>
+    <t>387/10/333</t>
+  </si>
+  <si>
+    <t>387/10/334</t>
+  </si>
+  <si>
+    <t>387/10/335</t>
+  </si>
+  <si>
+    <t>387/10/336</t>
+  </si>
+  <si>
+    <t>7/1/1</t>
+  </si>
+  <si>
+    <t>7/1/3</t>
+  </si>
+  <si>
+    <t>7/1/5</t>
+  </si>
+  <si>
+    <t>7/1/7</t>
+  </si>
+  <si>
+    <t>7/1/9</t>
+  </si>
+  <si>
+    <t>7/1/11</t>
+  </si>
+  <si>
+    <t>7/1/13</t>
+  </si>
+  <si>
+    <t>7/1/15</t>
+  </si>
+  <si>
+    <t>7/1/17</t>
+  </si>
+  <si>
+    <t>7/1/19</t>
+  </si>
+  <si>
+    <t>7/1/21</t>
+  </si>
+  <si>
+    <t>7/1/23</t>
+  </si>
+  <si>
+    <t>7/1/25</t>
+  </si>
+  <si>
+    <t>7/1/27</t>
+  </si>
+  <si>
+    <t>7/1/29</t>
+  </si>
+  <si>
+    <t>7/1/31</t>
+  </si>
+  <si>
+    <t>7/1/33</t>
+  </si>
+  <si>
+    <t>7/1/35</t>
+  </si>
+  <si>
+    <t>7/1/37</t>
+  </si>
+  <si>
+    <t>7/1/39</t>
+  </si>
+  <si>
+    <t>7/1/41</t>
+  </si>
+  <si>
+    <t>7/1/43</t>
+  </si>
+  <si>
+    <t>7/1/45</t>
+  </si>
+  <si>
+    <t>7/1/47</t>
+  </si>
+  <si>
+    <t>7/1/2</t>
+  </si>
+  <si>
+    <t>7/1/4</t>
+  </si>
+  <si>
+    <t>7/1/6</t>
+  </si>
+  <si>
+    <t>7/1/8</t>
+  </si>
+  <si>
+    <t>7/1/10</t>
+  </si>
+  <si>
+    <t>7/1/12</t>
+  </si>
+  <si>
+    <t>7/1/14</t>
+  </si>
+  <si>
+    <t>7/1/16</t>
+  </si>
+  <si>
+    <t>7/1/18</t>
+  </si>
+  <si>
+    <t>7/1/20</t>
+  </si>
+  <si>
+    <t>7/1/22</t>
+  </si>
+  <si>
+    <t>7/1/24</t>
+  </si>
+  <si>
+    <t>7/1/26</t>
+  </si>
+  <si>
+    <t>7/1/28</t>
+  </si>
+  <si>
+    <t>7/1/30</t>
+  </si>
+  <si>
+    <t>7/1/32</t>
+  </si>
+  <si>
+    <t>7/1/34</t>
+  </si>
+  <si>
+    <t>7/1/36</t>
+  </si>
+  <si>
+    <t>7/1/38</t>
+  </si>
+  <si>
+    <t>7/1/40</t>
+  </si>
+  <si>
+    <t>7/1/42</t>
+  </si>
+  <si>
+    <t>7/1/44</t>
+  </si>
+  <si>
+    <t>7/1/46</t>
+  </si>
+  <si>
+    <t>7/1/48</t>
   </si>
 </sst>
 </file>
@@ -1805,7 +2093,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1841,17 +2129,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2187,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E56308FB-24C0-497C-B992-8AC345332C81}">
-  <dimension ref="A1:C301"/>
+  <dimension ref="A1:C337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2208,3218 +2513,3699 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>322</v>
+        <v>361</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C136" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>392</v>
+        <v>431</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C141" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>393</v>
+        <v>432</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C144" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>398</v>
+        <v>437</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C152" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C153" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C154" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C155" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C156" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C157" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C158" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C159" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C160" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C161" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C162" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C163" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C164" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>416</v>
+        <v>455</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C165" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C166" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C167" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>166</v>
       </c>
       <c r="C168" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>420</v>
+        <v>459</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C169" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C170" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C171" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C172" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C173" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>172</v>
       </c>
       <c r="C174" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>173</v>
       </c>
       <c r="C175" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C176" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C177" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>176</v>
       </c>
       <c r="C178" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C179" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C180" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C181" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C182" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>181</v>
       </c>
       <c r="C183" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C184" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C185" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C186" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C187" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C188" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C189" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>188</v>
       </c>
       <c r="C190" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C191" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C192" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C193" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>192</v>
       </c>
       <c r="C194" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C195" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C196" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C197" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>196</v>
       </c>
       <c r="C198" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C199" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C200" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C201" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>200</v>
       </c>
       <c r="C202" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>201</v>
       </c>
       <c r="C203" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C204" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>203</v>
       </c>
       <c r="C205" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C206" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>458</v>
+        <v>497</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C207" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>206</v>
       </c>
       <c r="C208" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C209" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C210" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C211" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C212" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>464</v>
+        <v>503</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>211</v>
       </c>
       <c r="C213" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>212</v>
       </c>
       <c r="C214" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C215" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C216" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C217" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C218" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C219" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>471</v>
+        <v>510</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C220" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>472</v>
+        <v>511</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C221" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C222" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>221</v>
       </c>
       <c r="C223" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C224" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>476</v>
+        <v>515</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C225" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>224</v>
       </c>
       <c r="C226" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C227" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>226</v>
       </c>
       <c r="C228" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C229" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C230" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>229</v>
       </c>
       <c r="C231" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C232" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C233" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C234" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C235" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C236" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C237" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C238" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C239" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C240" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C241" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C242" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>241</v>
       </c>
       <c r="C243" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C244" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>243</v>
       </c>
       <c r="C245" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>244</v>
       </c>
       <c r="C246" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>245</v>
       </c>
       <c r="C247" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>246</v>
       </c>
       <c r="C248" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C249" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C250" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>249</v>
       </c>
       <c r="C251" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>525</v>
+        <v>253</v>
       </c>
       <c r="C252" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>526</v>
+        <v>254</v>
       </c>
       <c r="C253" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>527</v>
+        <v>255</v>
       </c>
       <c r="C254" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>528</v>
+        <v>256</v>
       </c>
       <c r="C255" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>529</v>
+        <v>257</v>
       </c>
       <c r="C256" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>530</v>
+        <v>258</v>
       </c>
       <c r="C257" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>531</v>
+        <v>259</v>
       </c>
       <c r="C258" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>532</v>
+        <v>260</v>
       </c>
       <c r="C259" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>533</v>
+        <v>261</v>
       </c>
       <c r="C260" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>512</v>
+        <v>551</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>534</v>
+        <v>262</v>
       </c>
       <c r="C261" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>535</v>
+        <v>263</v>
       </c>
       <c r="C262" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>536</v>
+        <v>264</v>
       </c>
       <c r="C263" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>537</v>
+        <v>265</v>
       </c>
       <c r="C264" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>516</v>
+        <v>555</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>538</v>
+        <v>266</v>
       </c>
       <c r="C265" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>555</v>
+        <v>267</v>
       </c>
       <c r="C266" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>518</v>
+        <v>557</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>556</v>
+        <v>268</v>
       </c>
       <c r="C267" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>557</v>
+        <v>269</v>
       </c>
       <c r="C268" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>558</v>
+        <v>270</v>
       </c>
       <c r="C269" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>559</v>
+        <v>271</v>
       </c>
       <c r="C270" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>560</v>
+        <v>272</v>
       </c>
       <c r="C271" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>561</v>
+        <v>273</v>
       </c>
       <c r="C272" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>562</v>
+        <v>274</v>
       </c>
       <c r="C273" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>563</v>
+        <v>275</v>
       </c>
       <c r="C274" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>564</v>
+        <v>276</v>
       </c>
       <c r="C275" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>565</v>
+        <v>277</v>
       </c>
       <c r="C276" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>566</v>
+        <v>278</v>
       </c>
       <c r="C277" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>567</v>
+        <v>279</v>
       </c>
       <c r="C278" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>568</v>
+        <v>280</v>
       </c>
       <c r="C279" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>569</v>
+        <v>281</v>
       </c>
       <c r="C280" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>570</v>
+        <v>282</v>
       </c>
       <c r="C281" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>571</v>
+        <v>283</v>
       </c>
       <c r="C282" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>572</v>
+        <v>284</v>
       </c>
       <c r="C283" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>573</v>
+        <v>285</v>
       </c>
       <c r="C284" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>574</v>
+        <v>286</v>
       </c>
       <c r="C285" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>575</v>
+        <v>287</v>
       </c>
       <c r="C286" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>576</v>
+        <v>288</v>
       </c>
       <c r="C287" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>577</v>
+        <v>289</v>
       </c>
       <c r="C288" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>578</v>
+        <v>290</v>
       </c>
       <c r="C289" t="s">
-        <v>579</v>
+        <v>291</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="4"/>
-      <c r="B290" s="2"/>
+      <c r="A290" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="C290" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="4"/>
-      <c r="B291" s="2"/>
+      <c r="A291" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C291" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="4"/>
-      <c r="B292" s="2"/>
+      <c r="A292" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="C292" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="4"/>
-      <c r="B293" s="2"/>
+      <c r="A293" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="C293" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="4"/>
-      <c r="B294" s="2"/>
+      <c r="A294" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C294" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="4"/>
-      <c r="B295" s="2"/>
+      <c r="A295" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="C295" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="4"/>
-      <c r="B296" s="2"/>
+      <c r="A296" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C296" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="4"/>
-      <c r="B297" s="2"/>
+      <c r="A297" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="C297" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="4"/>
-      <c r="B298" s="2"/>
+      <c r="A298" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C298" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="4"/>
-      <c r="B299" s="2"/>
+      <c r="A299" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C299" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="4"/>
-      <c r="B300" s="2"/>
+      <c r="A300" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C300" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="2"/>
+      <c r="A301" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C301" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C302" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C303" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C304" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C305" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C306" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="C307" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="C308" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="C309" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="C310" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C311" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="C312" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C313" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="C314" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="C315" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C316" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C317" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C318" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="C319" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C320" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="C321" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="C322" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C323" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C324" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="C325" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="C326" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C327" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C328" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="C329" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="C330" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C331" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C332" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C333" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C334" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C335" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C336" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="C337" t="s">
+        <v>291</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
